--- a/Basisordner/Simulationsvarianten.xlsx
+++ b/Basisordner/Simulationsvarianten.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\pierre\PycharmProjects\TimberBioC\Basisordner\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{688BA8D9-847F-4434-A40C-8B954CBB2045}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3237B701-BE57-4F33-B271-D6D082EA166B}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="25200" windowHeight="11175" xr2:uid="{A8D29AD5-9E31-46F4-AC48-A6B037963A8B}"/>
   </bookViews>
@@ -25,10 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10" uniqueCount="9">
-  <si>
-    <t>Name</t>
-  </si>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="21" uniqueCount="16">
   <si>
     <t>Pressure</t>
   </si>
@@ -42,16 +39,40 @@
     <t>S3</t>
   </si>
   <si>
-    <t>File1</t>
-  </si>
-  <si>
-    <t>File2</t>
-  </si>
-  <si>
     <t>Wetterdaten</t>
   </si>
   <si>
     <t>DENSITY</t>
+  </si>
+  <si>
+    <t>Wetter1</t>
+  </si>
+  <si>
+    <t>Wetter2</t>
+  </si>
+  <si>
+    <t>Parameter</t>
+  </si>
+  <si>
+    <t>File</t>
+  </si>
+  <si>
+    <t>b18</t>
+  </si>
+  <si>
+    <t>dck</t>
+  </si>
+  <si>
+    <t>t_T_MIN</t>
+  </si>
+  <si>
+    <t>b18_1</t>
+  </si>
+  <si>
+    <t>b18_2</t>
+  </si>
+  <si>
+    <t>b18_3</t>
   </si>
 </sst>
 </file>
@@ -403,63 +424,109 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CA0F8928-9CC2-453B-A914-4A72420974B3}">
-  <dimension ref="A1:D4"/>
+  <dimension ref="A1:E6"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C1" t="s">
+        <v>1</v>
+      </c>
+      <c r="D1" t="s">
+        <v>2</v>
+      </c>
+      <c r="E1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>4</v>
+      </c>
+      <c r="B2" t="s">
+        <v>4</v>
+      </c>
+      <c r="C2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D2" t="s">
+        <v>7</v>
+      </c>
+      <c r="E2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>10</v>
+      </c>
+      <c r="B3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C3" t="s">
+        <v>13</v>
+      </c>
+      <c r="D3" t="s">
+        <v>14</v>
+      </c>
+      <c r="E3" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>11</v>
+      </c>
+      <c r="B4" t="s">
+        <v>5</v>
+      </c>
+      <c r="C4">
+        <v>1036</v>
+      </c>
+      <c r="D4">
+        <v>1110</v>
+      </c>
+      <c r="E4">
+        <v>1184</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>11</v>
+      </c>
+      <c r="B5" t="s">
         <v>0</v>
       </c>
-      <c r="B1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C1" t="s">
-        <v>8</v>
-      </c>
-      <c r="D1" t="s">
-        <v>1</v>
+      <c r="C5">
+        <v>1369</v>
+      </c>
+      <c r="D5">
+        <v>1387.5</v>
+      </c>
+      <c r="E5">
+        <v>1406</v>
       </c>
     </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
-        <v>2</v>
-      </c>
-      <c r="B2" t="s">
-        <v>5</v>
-      </c>
-      <c r="C2">
-        <v>111</v>
-      </c>
-      <c r="D2">
-        <v>222</v>
-      </c>
-    </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
-        <v>3</v>
-      </c>
-      <c r="B3" t="s">
-        <v>6</v>
-      </c>
-      <c r="C3">
-        <v>333</v>
-      </c>
-      <c r="D3">
-        <v>444</v>
-      </c>
-    </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A4" t="s">
-        <v>4</v>
-      </c>
-      <c r="B4" t="s">
-        <v>6</v>
-      </c>
-      <c r="C4">
-        <v>555</v>
-      </c>
-      <c r="D4">
-        <v>666</v>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>11</v>
+      </c>
+      <c r="B6" t="s">
+        <v>12</v>
+      </c>
+      <c r="C6">
+        <v>1702</v>
+      </c>
+      <c r="D6">
+        <v>1665</v>
+      </c>
+      <c r="E6">
+        <v>1628</v>
       </c>
     </row>
   </sheetData>

--- a/Basisordner/Simulationsvarianten.xlsx
+++ b/Basisordner/Simulationsvarianten.xlsx
@@ -8,13 +8,17 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\pierre\PycharmProjects\TimberBioC\Basisordner\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3237B701-BE57-4F33-B271-D6D082EA166B}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{81C47CC1-D61B-4E8A-8531-FF2EE52DFDFA}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="25200" windowHeight="11175" xr2:uid="{A8D29AD5-9E31-46F4-AC48-A6B037963A8B}"/>
   </bookViews>
   <sheets>
     <sheet name="Simulationsvarianten" sheetId="1" r:id="rId1"/>
+    <sheet name="Liste" sheetId="2" r:id="rId2"/>
   </sheets>
+  <definedNames>
+    <definedName name="Wetterdaten">Liste!$A$1:$A$8</definedName>
+  </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
@@ -25,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="21" uniqueCount="16">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="27" uniqueCount="22">
   <si>
     <t>Pressure</t>
   </si>
@@ -45,12 +49,6 @@
     <t>DENSITY</t>
   </si>
   <si>
-    <t>Wetter1</t>
-  </si>
-  <si>
-    <t>Wetter2</t>
-  </si>
-  <si>
     <t>Parameter</t>
   </si>
   <si>
@@ -73,6 +71,30 @@
   </si>
   <si>
     <t>b18_3</t>
+  </si>
+  <si>
+    <t>TRY2045_Mannheim_Stadtzentrum_494902084637_Jahr</t>
+  </si>
+  <si>
+    <t>TRY2045_Mannheim_Stadtzentrum_494902084637_Somm</t>
+  </si>
+  <si>
+    <t>TRY2045_Mannheim_Vorort_495100085489_Jahr</t>
+  </si>
+  <si>
+    <t>TRY2045_Mannheim_Vorort_495100085489_Somm</t>
+  </si>
+  <si>
+    <t>TRY2045_Potsdam_Stadtzentrum_523938130651_Jahr</t>
+  </si>
+  <si>
+    <t>TRY2045_Potsdam_Stadtzentrum_523938130651_Somm</t>
+  </si>
+  <si>
+    <t>TRY2045_Potsdam_Vorort_523845130645_Jahr</t>
+  </si>
+  <si>
+    <t>TRY2045_Potsdam_Vorort_523845130645_Somm</t>
   </si>
 </sst>
 </file>
@@ -125,6 +147,20 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{95567F57-F0D2-42D7-B39A-99DED3C4C6E2}" name="Tabelle1" displayName="Tabelle1" ref="A1:E6" totalsRowShown="0">
+  <autoFilter ref="A1:E6" xr:uid="{171B3D22-DF80-4887-8CF7-E0044334CAF0}"/>
+  <tableColumns count="5">
+    <tableColumn id="1" xr3:uid="{8BB65710-968C-4C3B-8FE8-1EC2C93DA48F}" name="File"/>
+    <tableColumn id="2" xr3:uid="{0D7FE63F-588C-40C8-A727-8483168AC117}" name="Parameter"/>
+    <tableColumn id="3" xr3:uid="{D7EEF019-8A1D-47A1-9198-7283CB508026}" name="S1"/>
+    <tableColumn id="6" xr3:uid="{5C567AC9-7393-46F6-AEAC-C76F37DC29BA}" name="S2"/>
+    <tableColumn id="7" xr3:uid="{F7F22A19-ACEC-4126-930B-7E31D285E84B}" name="S3"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -426,13 +462,18 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CA0F8928-9CC2-453B-A914-4A72420974B3}">
   <dimension ref="A1:E6"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="12.42578125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.5703125" customWidth="1"/>
+    <col min="3" max="5" width="52.42578125" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="B1" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="C1" t="s">
         <v>1</v>
@@ -448,85 +489,137 @@
       <c r="A2" t="s">
         <v>4</v>
       </c>
-      <c r="B2" t="s">
-        <v>4</v>
-      </c>
       <c r="C2" t="s">
-        <v>6</v>
+        <v>14</v>
       </c>
       <c r="D2" t="s">
-        <v>7</v>
+        <v>15</v>
       </c>
       <c r="E2" t="s">
-        <v>7</v>
+        <v>16</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>10</v>
-      </c>
-      <c r="B3" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="C3" t="s">
+        <v>11</v>
+      </c>
+      <c r="D3" t="s">
+        <v>12</v>
+      </c>
+      <c r="E3" t="s">
         <v>13</v>
-      </c>
-      <c r="D3" t="s">
-        <v>14</v>
-      </c>
-      <c r="E3" t="s">
-        <v>15</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="B4" t="s">
         <v>5</v>
       </c>
       <c r="C4">
-        <v>1036</v>
+        <v>1</v>
       </c>
       <c r="D4">
-        <v>1110</v>
+        <v>4</v>
       </c>
       <c r="E4">
-        <v>1184</v>
+        <v>7</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="B5" t="s">
         <v>0</v>
       </c>
       <c r="C5">
-        <v>1369</v>
+        <v>2</v>
       </c>
       <c r="D5">
-        <v>1387.5</v>
+        <v>5</v>
       </c>
       <c r="E5">
-        <v>1406</v>
+        <v>8</v>
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="B6" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="C6">
-        <v>1702</v>
+        <v>3</v>
       </c>
       <c r="D6">
-        <v>1665</v>
+        <v>6</v>
       </c>
       <c r="E6">
-        <v>1628</v>
+        <v>9</v>
+      </c>
+    </row>
+  </sheetData>
+  <dataValidations count="1">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C2:E2" xr:uid="{29C4352F-4888-42D1-A1E2-BCAE4F2F7F0C}">
+      <formula1 xml:space="preserve"> Wetterdaten</formula1>
+    </dataValidation>
+  </dataValidations>
+  <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
+  <tableParts count="1">
+    <tablePart r:id="rId1"/>
+  </tableParts>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F781D9CC-94FD-413C-A032-5890ED6956BB}">
+  <dimension ref="A1:A8"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetData>
+    <row r="1" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="3" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="4" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="5" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="6" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="7" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="8" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>21</v>
       </c>
     </row>
   </sheetData>

--- a/Basisordner/Simulationsvarianten.xlsx
+++ b/Basisordner/Simulationsvarianten.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\pierre\PycharmProjects\TimberBioC\Basisordner\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{81C47CC1-D61B-4E8A-8531-FF2EE52DFDFA}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{85E8892D-DAFF-40C7-AA2E-0189D78318F4}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="25200" windowHeight="11175" xr2:uid="{A8D29AD5-9E31-46F4-AC48-A6B037963A8B}"/>
   </bookViews>
@@ -29,26 +29,11 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="27" uniqueCount="22">
-  <si>
-    <t>Pressure</t>
-  </si>
-  <si>
-    <t>S1</t>
-  </si>
-  <si>
-    <t>S2</t>
-  </si>
-  <si>
-    <t>S3</t>
-  </si>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="40" uniqueCount="27">
   <si>
     <t>Wetterdaten</t>
   </si>
   <si>
-    <t>DENSITY</t>
-  </si>
-  <si>
     <t>Parameter</t>
   </si>
   <si>
@@ -61,18 +46,6 @@
     <t>dck</t>
   </si>
   <si>
-    <t>t_T_MIN</t>
-  </si>
-  <si>
-    <t>b18_1</t>
-  </si>
-  <si>
-    <t>b18_2</t>
-  </si>
-  <si>
-    <t>b18_3</t>
-  </si>
-  <si>
     <t>TRY2045_Mannheim_Stadtzentrum_494902084637_Jahr</t>
   </si>
   <si>
@@ -95,6 +68,48 @@
   </si>
   <si>
     <t>TRY2045_Potsdam_Vorort_523845130645_Somm</t>
+  </si>
+  <si>
+    <t>AT-Wien-Hohe-Warte-110350.tm2</t>
+  </si>
+  <si>
+    <t>Mannheim_DWD_warm-hour.tm2</t>
+  </si>
+  <si>
+    <t>Bruckverdichtet_3Zonen34cc_PHbetstatTabsBung.b17</t>
+  </si>
+  <si>
+    <t>Bruckverdichtet_3Zonen34cc_BestbetstatTabsBung.b17</t>
+  </si>
+  <si>
+    <t>1</t>
+  </si>
+  <si>
+    <t>2</t>
+  </si>
+  <si>
+    <t>3</t>
+  </si>
+  <si>
+    <t>4</t>
+  </si>
+  <si>
+    <t>5</t>
+  </si>
+  <si>
+    <t>6</t>
+  </si>
+  <si>
+    <t>7</t>
+  </si>
+  <si>
+    <t>8</t>
+  </si>
+  <si>
+    <t>fen1</t>
+  </si>
+  <si>
+    <t>fen3</t>
   </si>
 </sst>
 </file>
@@ -130,7 +145,8 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
@@ -150,14 +166,19 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{95567F57-F0D2-42D7-B39A-99DED3C4C6E2}" name="Tabelle1" displayName="Tabelle1" ref="A1:E6" totalsRowShown="0">
-  <autoFilter ref="A1:E6" xr:uid="{171B3D22-DF80-4887-8CF7-E0044334CAF0}"/>
-  <tableColumns count="5">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{95567F57-F0D2-42D7-B39A-99DED3C4C6E2}" name="Tabelle1" displayName="Tabelle1" ref="A1:J5" totalsRowShown="0">
+  <autoFilter ref="A1:J5" xr:uid="{171B3D22-DF80-4887-8CF7-E0044334CAF0}"/>
+  <tableColumns count="10">
     <tableColumn id="1" xr3:uid="{8BB65710-968C-4C3B-8FE8-1EC2C93DA48F}" name="File"/>
     <tableColumn id="2" xr3:uid="{0D7FE63F-588C-40C8-A727-8483168AC117}" name="Parameter"/>
-    <tableColumn id="3" xr3:uid="{D7EEF019-8A1D-47A1-9198-7283CB508026}" name="S1"/>
-    <tableColumn id="6" xr3:uid="{5C567AC9-7393-46F6-AEAC-C76F37DC29BA}" name="S2"/>
-    <tableColumn id="7" xr3:uid="{F7F22A19-ACEC-4126-930B-7E31D285E84B}" name="S3"/>
+    <tableColumn id="3" xr3:uid="{D7EEF019-8A1D-47A1-9198-7283CB508026}" name="1"/>
+    <tableColumn id="6" xr3:uid="{5C567AC9-7393-46F6-AEAC-C76F37DC29BA}" name="2"/>
+    <tableColumn id="7" xr3:uid="{F7F22A19-ACEC-4126-930B-7E31D285E84B}" name="3"/>
+    <tableColumn id="4" xr3:uid="{458F436C-2D6C-426D-89EE-67407A986192}" name="4"/>
+    <tableColumn id="5" xr3:uid="{08F39B87-2CBF-4BB2-BC0B-CE24D1AF8518}" name="5"/>
+    <tableColumn id="8" xr3:uid="{4F6B50C3-51D6-4251-A309-70797087345E}" name="6"/>
+    <tableColumn id="9" xr3:uid="{E4308095-DA0B-4FDE-A323-F4B4870717B4}" name="7"/>
+    <tableColumn id="10" xr3:uid="{75F102DB-12FC-4DA1-8BB4-91367F7DE7FD}" name="8"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -460,7 +481,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CA0F8928-9CC2-453B-A914-4A72420974B3}">
-  <dimension ref="A1:E6"/>
+  <dimension ref="A1:J5"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="12.42578125" bestFit="1" customWidth="1"/>
@@ -468,100 +489,158 @@
     <col min="3" max="5" width="52.42578125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="B1" t="s">
-        <v>6</v>
-      </c>
-      <c r="C1" t="s">
         <v>1</v>
       </c>
-      <c r="D1" t="s">
-        <v>2</v>
-      </c>
-      <c r="E1" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="C1" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="2" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
+        <v>0</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="D2" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="E2" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="F2" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="G2" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="H2" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="I2" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="J2" s="1" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="3" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>3</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="D3" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="E3" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="F3" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="G3" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="H3" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="I3" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="J3" s="1" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="4" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
         <v>4</v>
       </c>
-      <c r="C2" t="s">
-        <v>14</v>
-      </c>
-      <c r="D2" t="s">
-        <v>15</v>
-      </c>
-      <c r="E2" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
-        <v>8</v>
-      </c>
-      <c r="C3" t="s">
-        <v>11</v>
-      </c>
-      <c r="D3" t="s">
-        <v>12</v>
-      </c>
-      <c r="E3" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A4" t="s">
-        <v>9</v>
-      </c>
       <c r="B4" t="s">
-        <v>5</v>
-      </c>
-      <c r="C4">
-        <v>1</v>
-      </c>
-      <c r="D4">
+        <v>25</v>
+      </c>
+      <c r="C4" s="1">
+        <v>0</v>
+      </c>
+      <c r="D4" s="1">
+        <v>3</v>
+      </c>
+      <c r="E4" s="1">
+        <v>0</v>
+      </c>
+      <c r="F4" s="1">
+        <v>3</v>
+      </c>
+      <c r="G4" s="1">
+        <v>0</v>
+      </c>
+      <c r="H4" s="1">
+        <v>3</v>
+      </c>
+      <c r="I4" s="1">
+        <v>0</v>
+      </c>
+      <c r="J4" s="1">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="5" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A5" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="E4">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A5" t="s">
-        <v>9</v>
-      </c>
-      <c r="B5" t="s">
-        <v>0</v>
-      </c>
-      <c r="C5">
-        <v>2</v>
-      </c>
-      <c r="D5">
-        <v>5</v>
-      </c>
-      <c r="E5">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A6" t="s">
-        <v>9</v>
-      </c>
-      <c r="B6" t="s">
-        <v>10</v>
-      </c>
-      <c r="C6">
-        <v>3</v>
-      </c>
-      <c r="D6">
-        <v>6</v>
-      </c>
-      <c r="E6">
-        <v>9</v>
+      <c r="B5" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="C5" s="1">
+        <v>0</v>
+      </c>
+      <c r="D5" s="1">
+        <v>3</v>
+      </c>
+      <c r="E5" s="1">
+        <v>0</v>
+      </c>
+      <c r="F5" s="1">
+        <v>3</v>
+      </c>
+      <c r="G5" s="1">
+        <v>0</v>
+      </c>
+      <c r="H5" s="1">
+        <v>3</v>
+      </c>
+      <c r="I5" s="1">
+        <v>0</v>
+      </c>
+      <c r="J5" s="1">
+        <v>3</v>
       </c>
     </row>
   </sheetData>
@@ -584,42 +663,42 @@
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>14</v>
+        <v>5</v>
       </c>
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>15</v>
+        <v>6</v>
       </c>
     </row>
     <row r="3" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>16</v>
+        <v>7</v>
       </c>
     </row>
     <row r="4" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>17</v>
+        <v>8</v>
       </c>
     </row>
     <row r="5" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>18</v>
+        <v>9</v>
       </c>
     </row>
     <row r="6" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>19</v>
+        <v>10</v>
       </c>
     </row>
     <row r="7" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>20</v>
+        <v>11</v>
       </c>
     </row>
     <row r="8" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>21</v>
+        <v>12</v>
       </c>
     </row>
   </sheetData>
